--- a/Documents/Product Catalog/Home/Bedroom Set Uv Print.xlsx
+++ b/Documents/Product Catalog/Home/Bedroom Set Uv Print.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A856B474-1D5A-4E46-ADD4-E236446467A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2697989-E50F-4F50-9702-1017BF6D588F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bedroom Set Uv Print " sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="157">
   <si>
     <t/>
   </si>
@@ -546,40 +546,79 @@
     <t>সূর্যমুখী বেড সাইড টেবিল</t>
   </si>
   <si>
-    <t>ডাবল বেড</t>
-  </si>
-  <si>
-    <t>বেড সাইড টেবিল</t>
-  </si>
-  <si>
-    <t>ড্রেসিং টেবিল</t>
-  </si>
-  <si>
     <t>সূর্যমুখী ড্রেসিং টেবিল</t>
   </si>
   <si>
-    <t>২-ডোর কাপবোর্ড</t>
-  </si>
-  <si>
-    <t>৩-ডোর কাপবোর্ড</t>
-  </si>
-  <si>
     <t>সূর্যমুখী ২-ডোর কাপবোর্ড</t>
   </si>
   <si>
     <t>সূর্যমুখী ৩-ডোর কাপবোর্ড</t>
   </si>
   <si>
-    <t>চেস্ট অফ ড্রয়ার</t>
-  </si>
-  <si>
-    <t>ওয়ারড্রোব</t>
-  </si>
-  <si>
     <t>সূর্যমুখী চেস্ট অফ ড্রয়ার</t>
   </si>
   <si>
     <t>সূর্যমুখী ওয়ারড্রোব</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল ডাবল বেড</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>রৌজা ডাবল বেড</t>
+  </si>
+  <si>
+    <t>রৌজা বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>কসমস ডাবল বেড</t>
+  </si>
+  <si>
+    <t>কসমস বেড সাইড টেবিল</t>
+  </si>
+  <si>
+    <t>কসমস ড্রেসিং টেবিল</t>
+  </si>
+  <si>
+    <t>রৌজা ড্রেসিং টেবিল</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল ড্রেসিং টেবিল</t>
+  </si>
+  <si>
+    <t>কসমস ২-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>কসমস ৩-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>রৌজা ২-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>রৌজা ৩-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল ২-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল ৩-ডোর কাপবোর্ড</t>
+  </si>
+  <si>
+    <t>কসমস ওয়ারড্রোব</t>
+  </si>
+  <si>
+    <t>রৌজা চেস্ট অফ ড্রয়ার</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল চেস্ট অফ ড্রয়ার</t>
+  </si>
+  <si>
+    <t>রৌজা ওয়ারড্রোব</t>
+  </si>
+  <si>
+    <t>ফ্লোরাল ওয়ারড্রোব</t>
   </si>
 </sst>
 </file>
@@ -954,23 +993,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -982,6 +1004,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3058,89 +3097,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
     </row>
     <row r="2" spans="1:46" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
     </row>
     <row r="3" spans="1:46" ht="50.1" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="42" t="s">
+      <c r="G3" s="52"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="49"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="42" t="s">
+      <c r="L3" s="52"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="42" t="s">
+      <c r="O3" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="P3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="42" t="s">
+      <c r="Q3" s="50" t="s">
         <v>14</v>
       </c>
       <c r="S3" s="4"/>
@@ -3173,11 +3212,11 @@
       <c r="AT3" s="4"/>
     </row>
     <row r="4" spans="1:46" ht="33.200000000000003" customHeight="1">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
       <c r="F4" s="27" t="s">
         <v>15</v>
       </c>
@@ -3187,8 +3226,8 @@
       <c r="H4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="46"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="49"/>
       <c r="K4" s="5" t="s">
         <v>18</v>
       </c>
@@ -3198,10 +3237,10 @@
       <c r="M4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -3239,7 +3278,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -3319,7 +3358,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
@@ -3399,7 +3438,7 @@
         <v>39</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="9" t="s">
@@ -3479,7 +3518,7 @@
         <v>41</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
@@ -3559,7 +3598,7 @@
         <v>44</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="9" t="s">
@@ -3639,7 +3678,7 @@
         <v>47</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="9" t="s">
@@ -3719,7 +3758,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="9" t="s">
@@ -3799,7 +3838,7 @@
         <v>51</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="9" t="s">
@@ -3879,7 +3918,7 @@
         <v>53</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="9" t="s">
@@ -3959,7 +3998,7 @@
         <v>61</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="9" t="s">
@@ -4039,7 +4078,7 @@
         <v>64</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="9" t="s">
@@ -4119,7 +4158,7 @@
         <v>67</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="9" t="s">
@@ -4199,7 +4238,7 @@
         <v>71</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="9" t="s">
@@ -4279,7 +4318,7 @@
         <v>79</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="9" t="s">
@@ -4359,7 +4398,7 @@
         <v>79</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="9" t="s">
@@ -4439,7 +4478,7 @@
         <v>85</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="9" t="s">
@@ -4519,7 +4558,7 @@
         <v>88</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="9" t="s">
@@ -4599,7 +4638,7 @@
         <v>88</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="9" t="s">
@@ -4679,7 +4718,7 @@
         <v>92</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="9" t="s">
@@ -4759,7 +4798,7 @@
         <v>94</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="9" t="s">
@@ -4839,7 +4878,7 @@
         <v>94</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="9" t="s">
@@ -4919,7 +4958,7 @@
         <v>97</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="9" t="s">
@@ -4999,7 +5038,7 @@
         <v>99</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="9" t="s">
@@ -5079,7 +5118,7 @@
         <v>99</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="9" t="s">
@@ -5159,7 +5198,7 @@
         <v>102</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="9" t="s">
@@ -5239,7 +5278,7 @@
         <v>109</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D30" s="29"/>
       <c r="E30" s="30" t="s">
@@ -5319,7 +5358,7 @@
         <v>113</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D31" s="29"/>
       <c r="E31" s="30" t="s">
@@ -5399,7 +5438,7 @@
         <v>117</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D32" s="29"/>
       <c r="E32" s="30" t="s">
@@ -5479,7 +5518,7 @@
         <v>120</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="9" t="s">
@@ -5559,7 +5598,7 @@
         <v>109</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="9" t="s">
@@ -5639,7 +5678,7 @@
         <v>126</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="9" t="s">
@@ -5719,7 +5758,7 @@
         <v>129</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="9" t="s">
